--- a/system_development/Damascus/V0.5.0/BOM-Damascus-V0.5.0.xlsx
+++ b/system_development/Damascus/V0.5.0/BOM-Damascus-V0.5.0.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\In-situ-monitoring-of-powder-bed-fusion-additive-manufacturing\system_development\Damascus\V0.5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adowney2\Documents\GitHub\In-situ-monitoring-of-powder-bed-fusion-additive-manufacturing\system_development\Damascus\V0.5.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D886170-94FA-42FC-AB7F-4BAC53439378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3766BD7C-0C69-4655-B857-7462819288DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
   <si>
     <t>Total Cost</t>
   </si>
@@ -321,17 +321,181 @@
   </si>
   <si>
     <t>https://www.cdwg.com/product/tripp-lite-1ft-augmented-cat6a-shielded-stp-snagless-patch-cable-blue-1ft/3726348</t>
+  </si>
+  <si>
+    <t>Thermal Camera</t>
+  </si>
+  <si>
+    <t>Optris Xi 400 thermal camera, 382 x 288, 18 deg x 14 deg lens, f = 20 mm</t>
+  </si>
+  <si>
+    <t>OPTXI40LTF20T090</t>
+  </si>
+  <si>
+    <t>Optional thermal-imaging configuration from paper; includes PIX Connect software/cables per vendor listing.</t>
+  </si>
+  <si>
+    <t>https://www.tequipment.net/Optris/XI400-18x14/Scientific-Thermal-Imagers/</t>
+  </si>
+  <si>
+    <t>https://optris.com/us/products/thermal-cameras/compact-line/xi-400/</t>
+  </si>
+  <si>
+    <t>https://www.newark.com/optris/optxi40ltf20t090/thermal-imager-382-x-288-20mm/dp/70AJ6214</t>
+  </si>
+  <si>
+    <t>Optical Camera - USB3</t>
+  </si>
+  <si>
+    <t>BFS-U3-200S6M-C USB 3.1 Blackfly S monochrome camera, 20 MP, 1 in Sony IMX183, C-Mount</t>
+  </si>
+  <si>
+    <t>BFS-U3-200S6M-C</t>
+  </si>
+  <si>
+    <t>Primary optical camera from paper; note that camera accessories/cables may be sold separately.</t>
+  </si>
+  <si>
+    <t>https://www.edmundoptics.com/p/BFS-U3-200S6M-C-USB3-Blackflyreg-S-Monochrome-Camera/40177/</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/flir-integrated-imaging-solutions-inc/BFS-U3-200S6M-C/16528419</t>
+  </si>
+  <si>
+    <t>Optical Camera - GigE/PoE Alternate</t>
+  </si>
+  <si>
+    <t>BFS-PGE-200S6M-C PoE GigE Blackfly S monochrome camera, 20 MP, 1 in Sony IMX183, C-Mount</t>
+  </si>
+  <si>
+    <t>BFS-PGE-200S6M-C</t>
+  </si>
+  <si>
+    <t>Optional alternate from supplied eBay link; set Amount Per Cover to 1 if selecting the PoE/GigE camera instead of USB3.</t>
+  </si>
+  <si>
+    <t>https://www.edmundoptics.com/p/bfs-pge-200s6m-c-poe-gige-blackflyr-s-monochrome-camera/40195/</t>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/388858412191</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/flir-integrated-imaging-solutions-inc/BFS-PGE-200S6M-C/16528297</t>
+  </si>
+  <si>
+    <t>35 mm Lens - 1 in Sensor</t>
+  </si>
+  <si>
+    <t>Edmund Optics 35 mm focal length HP Series fixed focal length lens, C-Mount, f/1.8, 1.1 in max sensor format</t>
+  </si>
+  <si>
+    <t>86-573</t>
+  </si>
+  <si>
+    <t>Primary high-resolution optical lens for the 1 in/20 MP camera; supplied eBay 86573 listing maps to Edmund stock #86-573.</t>
+  </si>
+  <si>
+    <t>https://www.edmundoptics.com/p/35mm-focal-length-hp-series-fixed-focal-length-lens/28992/</t>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/334656600752</t>
+  </si>
+  <si>
+    <t>35 mm Lens - 2/3 in Alternate</t>
+  </si>
+  <si>
+    <t>Edmund Optics 35 mm C Series fixed focal length lens, C-Mount, f/1.65, 2/3 in max sensor format</t>
+  </si>
+  <si>
+    <t>59-872</t>
+  </si>
+  <si>
+    <t>Optional older/used lens from duplicate eBay link; not counted in total unless selected. eBay sold listing showed $49.99.</t>
+  </si>
+  <si>
+    <t>https://www.edmundoptics.com/p/35mm-c-series-fixed-focal-length-lens/16529/</t>
+  </si>
+  <si>
+    <t>https://www.ebay.com/itm/377073297097</t>
+  </si>
+  <si>
+    <t>Lens Step-Up Adapter</t>
+  </si>
+  <si>
+    <t>Midwest Optical Systems Step-Up Adapter M25.5-M37</t>
+  </si>
+  <si>
+    <t>SU25.5-37</t>
+  </si>
+  <si>
+    <t>Use with the #59-872 C Series lens to mount M37 filters; not needed for the #86-573 HP lens with native M37 thread.</t>
+  </si>
+  <si>
+    <t>https://machinevisiondirect.com/products/midopt-su25_5-37?variant=37662128013502</t>
+  </si>
+  <si>
+    <t>Bandpass Filter - Dark Red 660 nm</t>
+  </si>
+  <si>
+    <t>Midwest Optical Systems BP660-37 dark red bandpass filter, M37 x P0.75</t>
+  </si>
+  <si>
+    <t>BP660-37</t>
+  </si>
+  <si>
+    <t>Paper-specified dark red bandpass filter; use with 650-680 nm red lighting.</t>
+  </si>
+  <si>
+    <t>https://machinevisiondirect.com/products/mid-bp660-37</t>
+  </si>
+  <si>
+    <t>https://midopt.com/filters/bp660/</t>
+  </si>
+  <si>
+    <t>Bandpass Filter - Light Red 635 nm</t>
+  </si>
+  <si>
+    <t>Midwest Optical Systems BP635-37 light red bandpass filter, M37 x P0.75</t>
+  </si>
+  <si>
+    <t>BP635-37</t>
+  </si>
+  <si>
+    <t>Optional light-red filter from supplied link; set Amount Per Cover to 1 for 615-645 nm lighting.</t>
+  </si>
+  <si>
+    <t>https://machinevisiondirect.com/products/mid-bp635-37</t>
+  </si>
+  <si>
+    <t>https://midopt.com/filters/bp635/</t>
+  </si>
+  <si>
+    <t>37 mm UV Protective Lens Filter</t>
+  </si>
+  <si>
+    <t>Tiffen UV Protector Filter, 37 mm</t>
+  </si>
+  <si>
+    <t>37UVP</t>
+  </si>
+  <si>
+    <t>Plain protective UV filter for 37 mm lens/filter thread</t>
+  </si>
+  <si>
+    <t>Tiffen</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -374,6 +538,22 @@
       <name val="Source Sans Pro"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -401,11 +581,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -438,10 +620,31 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink 2" xfId="3" xr:uid="{47B38DBD-1F5B-4A8C-867A-C157945EC6DB}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{9123710A-AD88-4C64-B627-92812002B346}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -773,7 +976,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
@@ -916,7 +1119,7 @@
       <c r="D5" s="2"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9">
-        <f t="shared" ref="F5:F32" si="1">D5*E5</f>
+        <f t="shared" ref="F5:F40" si="1">D5*E5</f>
         <v>0</v>
       </c>
       <c r="G5" s="5"/>
@@ -1386,7 +1589,7 @@
       <c r="E28" s="8">
         <v>329</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="9">
         <f t="shared" si="1"/>
         <v>329</v>
       </c>
@@ -1490,17 +1693,293 @@
         <v>92</v>
       </c>
     </row>
-    <row r="36" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-    </row>
-    <row r="37" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E37" s="7" t="s">
+    <row r="33" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="D33" s="15">
+        <v>1</v>
+      </c>
+      <c r="E33" s="16">
+        <v>2995</v>
+      </c>
+      <c r="F33" s="9">
+        <f t="shared" si="1"/>
+        <v>2995</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="H33" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="I33" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="D34" s="15">
+        <v>1</v>
+      </c>
+      <c r="E34" s="16">
+        <v>700</v>
+      </c>
+      <c r="F34" s="9">
+        <f t="shared" si="1"/>
+        <v>700</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="H34" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="I34" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="J34" s="14"/>
+    </row>
+    <row r="35" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="D35" s="15">
+        <v>1</v>
+      </c>
+      <c r="E35" s="16">
+        <v>700</v>
+      </c>
+      <c r="F35" s="9">
+        <f t="shared" si="1"/>
+        <v>700</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="H35" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="I35" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="J35" s="14" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="D36" s="15">
+        <v>1</v>
+      </c>
+      <c r="E36" s="16">
+        <v>660</v>
+      </c>
+      <c r="F36" s="9">
+        <f t="shared" si="1"/>
+        <v>660</v>
+      </c>
+      <c r="G36" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="H36" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="I36" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="J36" s="14"/>
+    </row>
+    <row r="37" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="D37" s="15">
+        <v>1</v>
+      </c>
+      <c r="E37" s="18">
+        <v>374</v>
+      </c>
+      <c r="F37" s="9">
+        <f t="shared" si="1"/>
+        <v>374</v>
+      </c>
+      <c r="G37" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="H37" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="I37" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="J37" s="14"/>
+    </row>
+    <row r="38" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="D38" s="15">
+        <v>1</v>
+      </c>
+      <c r="E38" s="16">
+        <v>30</v>
+      </c>
+      <c r="F38" s="9">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="G38" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="H38" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
+    </row>
+    <row r="39" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D39" s="15">
+        <v>1</v>
+      </c>
+      <c r="E39" s="16">
+        <v>151</v>
+      </c>
+      <c r="F39" s="9">
+        <f t="shared" si="1"/>
+        <v>151</v>
+      </c>
+      <c r="G39" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="H39" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="I39" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="J39" s="14"/>
+    </row>
+    <row r="40" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D40" s="15">
+        <v>1</v>
+      </c>
+      <c r="E40" s="16">
+        <v>151</v>
+      </c>
+      <c r="F40" s="9">
+        <f t="shared" si="1"/>
+        <v>151</v>
+      </c>
+      <c r="G40" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="H40" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="I40" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="J40" s="14"/>
+    </row>
+    <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C41" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="D41" s="19">
+        <v>1</v>
+      </c>
+      <c r="E41" s="20">
+        <v>9.99</v>
+      </c>
+      <c r="F41" s="20">
+        <v>9.99</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E43" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F37" s="5">
-        <f>SUM(F2:F36)</f>
-        <v>3069.9500000000003</v>
+      <c r="F43" s="5">
+        <f>SUM(F2:F42)</f>
+        <v>8840.94</v>
       </c>
     </row>
   </sheetData>

--- a/system_development/Damascus/V0.5.0/BOM-Damascus-V0.5.0.xlsx
+++ b/system_development/Damascus/V0.5.0/BOM-Damascus-V0.5.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adowney2\Documents\GitHub\In-situ-monitoring-of-powder-bed-fusion-additive-manufacturing\system_development\Damascus\V0.5.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3766BD7C-0C69-4655-B857-7462819288DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C80D5577-F5C0-4911-8014-BD3A5E7B868C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-16320" yWindow="-6540" windowWidth="16440" windowHeight="28320" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="148">
   <si>
     <t>Total Cost</t>
   </si>
@@ -281,12 +281,6 @@
     <t>10 GBE to Thunderbolt adapter</t>
   </si>
   <si>
-    <t>Eaton Tripp Lite Series Cat6a 10G Snagless Shielded STP Ethernet Cable (RJ45 M/M), PoE, Blue, 1 ft. (0.31 m) - patch</t>
-  </si>
-  <si>
-    <t>N262-001-BL</t>
-  </si>
-  <si>
     <t>OWC 1.0M (39.4") Thunderbolt 5 (USB-C) Cable Black for Thunderbolt And USB-C Devices - Black</t>
   </si>
   <si>
@@ -320,9 +314,6 @@
     <t>https://www.cdwg.com/product/owc-2.0m-78-thunderbolt-4-usb-c-cable-for-thunderbolt-and-usb-c-device/7390529</t>
   </si>
   <si>
-    <t>https://www.cdwg.com/product/tripp-lite-1ft-augmented-cat6a-shielded-stp-snagless-patch-cable-blue-1ft/3726348</t>
-  </si>
-  <si>
     <t>Thermal Camera</t>
   </si>
   <si>
@@ -483,6 +474,12 @@
   </si>
   <si>
     <t>Tiffen</t>
+  </si>
+  <si>
+    <t>https://www.cdwg.com/product/eaton-tripp-lite-series-cat6a-10g-snagless-shielded-slim-stp-ethernet-cable/7175130?pfm=srh</t>
+  </si>
+  <si>
+    <t>Eaton Tripp Lite Series Cat6a 10G Snagless Shielded Slim STP Ethernet Cable (RJ45 M/M), PoE, Blue, 3 ft. (0.9 m)</t>
   </si>
 </sst>
 </file>
@@ -587,7 +584,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -629,7 +626,6 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -1602,23 +1598,23 @@
         <v>79</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>82</v>
+        <v>147</v>
+      </c>
+      <c r="C29" s="13">
+        <v>7175130</v>
       </c>
       <c r="D29" s="2">
         <v>1</v>
       </c>
       <c r="E29" s="9">
-        <v>7.62</v>
+        <v>8.4700000000000006</v>
       </c>
       <c r="F29" s="9">
         <f t="shared" si="1"/>
-        <v>7.62</v>
+        <v>8.4700000000000006</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>94</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1626,10 +1622,10 @@
         <v>80</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D30" s="2">
         <v>1</v>
@@ -1642,18 +1638,18 @@
         <v>181.53</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31" t="s">
         <v>85</v>
-      </c>
-      <c r="C31" t="s">
-        <v>87</v>
       </c>
       <c r="D31" s="2">
         <v>1</v>
@@ -1666,18 +1662,18 @@
         <v>49.29</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C32" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D32" s="2">
         <v>1</v>
@@ -1690,18 +1686,18 @@
         <v>30.51</v>
       </c>
       <c r="H32" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="14" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="14" t="s">
-        <v>95</v>
-      </c>
       <c r="B33" s="14" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D33" s="15">
         <v>1</v>
@@ -1714,27 +1710,27 @@
         <v>2995</v>
       </c>
       <c r="G33" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="H33" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="I33" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="J33" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="H33" s="14" t="s">
+    </row>
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="I33" s="14" t="s">
+      <c r="B34" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="J33" s="14" t="s">
+      <c r="C34" s="14" t="s">
         <v>101</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>104</v>
       </c>
       <c r="D34" s="15">
         <v>1</v>
@@ -1747,25 +1743,25 @@
         <v>700</v>
       </c>
       <c r="G34" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="H34" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="I34" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="J34" s="14"/>
+    </row>
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="H34" s="14" t="s">
+      <c r="B35" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="I34" s="14" t="s">
+      <c r="C35" s="14" t="s">
         <v>107</v>
-      </c>
-      <c r="J34" s="14"/>
-    </row>
-    <row r="35" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>110</v>
       </c>
       <c r="D35" s="15">
         <v>1</v>
@@ -1778,27 +1774,27 @@
         <v>700</v>
       </c>
       <c r="G35" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="H35" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="I35" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="J35" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="H35" s="14" t="s">
+    </row>
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="I35" s="14" t="s">
+      <c r="B36" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="J35" s="14" t="s">
+      <c r="C36" s="14" t="s">
         <v>114</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="B36" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>117</v>
       </c>
       <c r="D36" s="15">
         <v>1</v>
@@ -1811,56 +1807,56 @@
         <v>660</v>
       </c>
       <c r="G36" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="H36" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="I36" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="J36" s="14"/>
+    </row>
+    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="H36" s="14" t="s">
+      <c r="B37" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="I36" s="14" t="s">
+      <c r="C37" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="J36" s="14"/>
-    </row>
-    <row r="37" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="14" t="s">
+      <c r="D37" s="15">
+        <v>1</v>
+      </c>
+      <c r="E37" s="17">
+        <v>374</v>
+      </c>
+      <c r="F37" s="9">
+        <f t="shared" si="1"/>
+        <v>374</v>
+      </c>
+      <c r="G37" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="B37" s="14" t="s">
+      <c r="H37" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="I37" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="D37" s="15">
-        <v>1</v>
-      </c>
-      <c r="E37" s="18">
-        <v>374</v>
-      </c>
-      <c r="F37" s="9">
-        <f t="shared" si="1"/>
-        <v>374</v>
-      </c>
-      <c r="G37" s="14" t="s">
+      <c r="J37" s="14"/>
+    </row>
+    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="H37" s="14" t="s">
+      <c r="B38" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="I37" s="14" t="s">
+      <c r="C38" s="14" t="s">
         <v>126</v>
-      </c>
-      <c r="J37" s="14"/>
-    </row>
-    <row r="38" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>129</v>
       </c>
       <c r="D38" s="15">
         <v>1</v>
@@ -1873,23 +1869,23 @@
         <v>30</v>
       </c>
       <c r="G38" s="14" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H38" s="14" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I38" s="14"/>
       <c r="J38" s="14"/>
     </row>
-    <row r="39" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D39" s="15">
         <v>1</v>
@@ -1902,25 +1898,25 @@
         <v>151</v>
       </c>
       <c r="G39" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="H39" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="I39" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="J39" s="14"/>
+    </row>
+    <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="H39" s="14" t="s">
+      <c r="B40" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="I39" s="14" t="s">
+      <c r="C40" s="14" t="s">
         <v>137</v>
-      </c>
-      <c r="J39" s="14"/>
-    </row>
-    <row r="40" spans="1:10" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="B40" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>140</v>
       </c>
       <c r="D40" s="15">
         <v>1</v>
@@ -1933,40 +1929,40 @@
         <v>151</v>
       </c>
       <c r="G40" s="14" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="H40" s="14" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="I40" s="14" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="J40" s="14"/>
     </row>
     <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C41" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="D41" s="18">
+        <v>1</v>
+      </c>
+      <c r="E41" s="19">
+        <v>9.99</v>
+      </c>
+      <c r="F41" s="19">
+        <v>9.99</v>
+      </c>
+      <c r="G41" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="H41" s="4" t="s">
         <v>145</v>
-      </c>
-      <c r="C41" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="D41" s="19">
-        <v>1</v>
-      </c>
-      <c r="E41" s="20">
-        <v>9.99</v>
-      </c>
-      <c r="F41" s="20">
-        <v>9.99</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -1979,7 +1975,7 @@
       </c>
       <c r="F43" s="5">
         <f>SUM(F2:F42)</f>
-        <v>8840.94</v>
+        <v>8841.7899999999991</v>
       </c>
     </row>
   </sheetData>
@@ -2000,9 +1996,8 @@
     <hyperlink ref="H30" r:id="rId13" xr:uid="{801BAFE3-F6D0-4BC5-8B21-256CC97C2787}"/>
     <hyperlink ref="H32" r:id="rId14" xr:uid="{48EA4B1F-CBAD-4590-9666-2342E248E6D7}"/>
     <hyperlink ref="H31" r:id="rId15" xr:uid="{009BE108-4464-476B-A6EC-083EA45298AB}"/>
-    <hyperlink ref="H29" r:id="rId16" xr:uid="{7AD70C87-5E84-47F4-BFB8-F408B6CD48AB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId17"/>
+  <pageSetup orientation="portrait" r:id="rId16"/>
 </worksheet>
 </file>